--- a/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,93</t>
+          <t>0,54; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,49; 55,18</t>
+          <t>19,98; 57,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,23</t>
+          <t>2,25; 9,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,06</t>
+          <t>0,47; 4,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 46,96</t>
+          <t>23,13; 49,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,29</t>
+          <t>1,78; 6,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,66</t>
+          <t>0,25; 2,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,83; 45,91</t>
+          <t>24,2; 46,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,9; 35,77</t>
+          <t>14,15; 37,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,46</t>
+          <t>0,33; 3,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 21,4</t>
+          <t>10,3; 21,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,86</t>
+          <t>0,18; 1,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,28</t>
+          <t>0,14; 1,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,84</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,71; 24,37</t>
+          <t>14,22; 24,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,46; 44,1</t>
+          <t>19,31; 44,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,59; 42,9</t>
+          <t>25,22; 43,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,23; 2,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 40,29</t>
+          <t>25,28; 40,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 42,06</t>
+          <t>14,47; 40,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,71</t>
+          <t>0,63; 3,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,23</t>
+          <t>0,35; 3,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 25,59</t>
+          <t>13,25; 26,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,09</t>
+          <t>0,35; 2,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,19; 1,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 29,26</t>
+          <t>15,74; 30,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,21</t>
+          <t>0,79; 9,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,07</t>
+          <t>0,77; 8,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 29,16</t>
+          <t>7,21; 30,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,22; 33,17</t>
+          <t>16,05; 35,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,15</t>
+          <t>0,81; 5,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,0</t>
+          <t>0,36; 3,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 28,85</t>
+          <t>14,53; 28,73</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,08</t>
+          <t>0,5; 4,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,53; 31,8</t>
+          <t>14,51; 32,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,05; 33,22</t>
+          <t>19,36; 32,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,2</t>
+          <t>0,32; 2,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,77; 30,2</t>
+          <t>19,39; 30,48</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,25</t>
+          <t>0,26; 3,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 21,31</t>
+          <t>4,44; 19,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,73</t>
+          <t>0,66; 2,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,89</t>
+          <t>0,22; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 21,71</t>
+          <t>0,77; 22,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,43</t>
+          <t>0,63; 2,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,58</t>
+          <t>0,25; 1,46</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 17,26</t>
+          <t>1,26; 17,6</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,42</t>
+          <t>0,22; 2,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,25</t>
+          <t>0,24; 2,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,26</t>
+          <t>1,85; 6,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,34</t>
+          <t>0,3; 2,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,88</t>
+          <t>0,55; 2,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,08</t>
+          <t>5,91; 11,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,89</t>
+          <t>0,41; 1,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,11</t>
+          <t>0,54; 1,91</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,45</t>
+          <t>4,79; 8,44</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,08</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,25</t>
+          <t>0,46; 1,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,43</t>
+          <t>0,57; 1,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,68; 20,03</t>
+          <t>13,65; 20,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,29</t>
+          <t>0,44; 1,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,66</t>
+          <t>0,72; 1,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,54</t>
+          <t>0,64; 1,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,09</t>
+          <t>7,22; 18,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,06</t>
+          <t>0,44; 0,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,32</t>
+          <t>0,68; 1,32</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,29</t>
+          <t>0,66; 1,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,71</t>
+          <t>8,58; 17,73</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6300</t>
+          <t>0; 6242</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>966; 10541</t>
+          <t>953; 8967</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5347</t>
+          <t>0; 5704</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4858; 13755</t>
+          <t>4981; 14321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2055</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4006; 19270</t>
+          <t>4693; 19618</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>937; 8133</t>
+          <t>933; 8678</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6902; 14513</t>
+          <t>7150; 15324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6920</t>
+          <t>0; 6330</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7454; 24299</t>
+          <t>6887; 24697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1028; 9941</t>
+          <t>951; 9061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13867; 25637</t>
+          <t>13514; 25986</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4856</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8357</t>
+          <t>0; 7359</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9684; 24926</t>
+          <t>9858; 26034</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1188; 12261</t>
+          <t>1179; 12180</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7558</t>
+          <t>0; 7510</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7680</t>
+          <t>0; 7373</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12100; 24072</t>
+          <t>11585; 23647</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1744; 11925</t>
+          <t>1174; 11939</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>944; 8611</t>
+          <t>951; 9111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1084; 10752</t>
+          <t>1021; 10404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24982; 44397</t>
+          <t>25914; 45066</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5575</t>
+          <t>0; 4987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8881; 19140</t>
+          <t>8380; 19196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7152</t>
+          <t>0; 7313</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 8891</t>
+          <t>0; 8337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 5983</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14161; 25753</t>
+          <t>15138; 26103</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7460</t>
+          <t>0; 6536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 8800</t>
+          <t>0; 8396</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7719</t>
+          <t>894; 7826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26132; 41673</t>
+          <t>26144; 42071</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5269</t>
+          <t>0; 5886</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8905; 25254</t>
+          <t>8689; 24537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1838</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1821; 10865</t>
+          <t>1850; 10624</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>882; 8259</t>
+          <t>882; 8409</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10179; 19522</t>
+          <t>10108; 20036</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5440</t>
+          <t>0; 5894</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1902; 11211</t>
+          <t>1879; 10955</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>883; 8216</t>
+          <t>871; 7619</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21208; 39892</t>
+          <t>21459; 41040</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>850; 9952</t>
+          <t>850; 9786</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 10864</t>
+          <t>0; 13888</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1000; 10804</t>
+          <t>1026; 11154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1562; 6527</t>
+          <t>1615; 6730</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8548</t>
+          <t>0; 7327</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1886</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4723; 10295</t>
+          <t>4981; 10889</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1860; 13273</t>
+          <t>2088; 13659</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 10999</t>
+          <t>0; 10973</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1009; 11179</t>
+          <t>1008; 11036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7429; 15413</t>
+          <t>7759; 15347</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5880</t>
+          <t>0; 6493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>803; 8190</t>
+          <t>809; 8042</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8279; 18119</t>
+          <t>8264; 18596</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7718</t>
+          <t>0; 7132</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1980</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6976</t>
+          <t>0; 5981</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13485; 23521</t>
+          <t>13710; 23264</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7955</t>
+          <t>0; 8266</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 6769</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1251; 10639</t>
+          <t>1080; 9835</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23983; 38585</t>
+          <t>24773; 38948</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1099; 12889</t>
+          <t>1015; 12871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7519</t>
+          <t>0; 7716</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2147; 10310</t>
+          <t>2149; 9401</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4979</t>
+          <t>0; 4970</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2187; 12456</t>
+          <t>3011; 13618</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>966; 8377</t>
+          <t>958; 8411</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1636; 57714</t>
+          <t>2054; 58498</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5608</t>
+          <t>0; 5534</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5284; 20712</t>
+          <t>5402; 21078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2063; 12417</t>
+          <t>1992; 11433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2773; 54254</t>
+          <t>3953; 55304</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1015; 11256</t>
+          <t>1024; 12806</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6082</t>
+          <t>0; 6541</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>937; 10272</t>
+          <t>1085; 10056</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2594; 10237</t>
+          <t>3023; 10483</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1648; 12599</t>
+          <t>1639; 12865</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 7779</t>
+          <t>0; 7744</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3805; 16813</t>
+          <t>3232; 16071</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15032; 27638</t>
+          <t>14727; 27535</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3870; 18963</t>
+          <t>4149; 18257</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1045; 9448</t>
+          <t>1046; 10364</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6309; 22006</t>
+          <t>5587; 19842</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19680; 34873</t>
+          <t>19775; 34838</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4736; 20677</t>
+          <t>5479; 20075</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9457; 26765</t>
+          <t>9727; 28419</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10603; 27109</t>
+          <t>10835; 27175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66947; 97983</t>
+          <t>66767; 99445</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10664; 29730</t>
+          <t>10194; 28173</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18997; 41757</t>
+          <t>18056; 41584</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14413; 35890</t>
+          <t>14921; 33490</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>57911; 162248</t>
+          <t>64709; 162854</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19490; 44763</t>
+          <t>18664; 41428</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32174; 61541</t>
+          <t>31692; 61375</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29413; 54728</t>
+          <t>28035; 54523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>120183; 245408</t>
+          <t>118878; 245815</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,05</t>
+          <t>0,55; 4,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 57,45</t>
+          <t>16,53; 51,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,4</t>
+          <t>2,28; 9,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,33</t>
+          <t>0,46; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,13; 49,58</t>
+          <t>20,66; 43,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,39</t>
+          <t>1,93; 6,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,42</t>
+          <t>0,28; 2,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,2; 46,54</t>
+          <t>22,87; 41,87</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 37,36</t>
+          <t>12,92; 34,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,44</t>
+          <t>0,51; 3,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,02</t>
+          <t>10,21; 20,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,86</t>
+          <t>0,18; 1,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,35</t>
+          <t>0,14; 1,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,19; 2,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 24,74</t>
+          <t>13,03; 24,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 44,23</t>
+          <t>17,82; 41,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,22; 43,48</t>
+          <t>24,68; 43,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,01</t>
+          <t>0,23; 1,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,28; 40,67</t>
+          <t>25,17; 40,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 40,87</t>
+          <t>12,73; 38,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,63</t>
+          <t>0,64; 3,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,29</t>
+          <t>0,34; 3,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 26,26</t>
+          <t>11,67; 23,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,04</t>
+          <t>0,34; 2,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,7</t>
+          <t>0,2; 1,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 30,1</t>
+          <t>14,83; 29,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,05</t>
+          <t>0,78; 9,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,57</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 8,34</t>
+          <t>1,22; 8,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 30,07</t>
+          <t>6,2; 27,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,05; 35,09</t>
+          <t>13,97; 32,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,3</t>
+          <t>0,83; 5,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,95</t>
+          <t>0,36; 3,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 28,73</t>
+          <t>12,95; 26,67</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,99</t>
+          <t>0,5; 4,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,51; 32,64</t>
+          <t>14,02; 30,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,36; 32,86</t>
+          <t>19,05; 33,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,95</t>
+          <t>0,29; 2,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,39; 30,48</t>
+          <t>18,8; 29,57</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -1557,42 +1557,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,24</t>
+          <t>0,49; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 19,43</t>
+          <t>4,72; 21,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,98</t>
+          <t>0,48; 2,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,9</t>
+          <t>0,22; 1,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 22,0</t>
+          <t>12,5; 29,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,47</t>
+          <t>0,72; 2,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,46</t>
+          <t>0,26; 1,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 17,6</t>
+          <t>10,84; 23,68</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,75</t>
+          <t>0,22; 2,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,37 +1707,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,2</t>
+          <t>0,24; 2,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,41</t>
+          <t>1,68; 6,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,39</t>
+          <t>0,22; 2,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,75</t>
+          <t>0,66; 2,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,04</t>
+          <t>5,91; 11,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,82</t>
+          <t>0,36; 1,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,91</t>
+          <t>0,64; 2,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,44</t>
+          <t>4,77; 8,46</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,32; 1,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,33</t>
+          <t>0,44; 1,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,43</t>
+          <t>0,55; 1,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,33</t>
+          <t>12,54; 18,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,22</t>
+          <t>0,46; 1,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,65</t>
+          <t>0,78; 1,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,43</t>
+          <t>0,63; 1,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,16</t>
+          <t>14,65; 18,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,98</t>
+          <t>0,44; 0,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,32</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,69; 1,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,73</t>
+          <t>14,42; 17,87</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19357</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6242</t>
+          <t>0; 6335</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>953; 8967</t>
+          <t>980; 8712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>0; 6108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4981; 14321</t>
+          <t>4192; 13090</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4693; 19618</t>
+          <t>4754; 19965</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>933; 8678</t>
+          <t>926; 6940</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7150; 15324</t>
+          <t>7230; 15386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6330</t>
+          <t>0; 6247</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6887; 24697</t>
+          <t>7462; 24985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>951; 9061</t>
+          <t>1029; 9376</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13514; 25986</t>
+          <t>13800; 25269</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>36066</t>
         </is>
       </c>
     </row>
@@ -2422,57 +2422,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 4781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7359</t>
+          <t>0; 7828</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9858; 26034</t>
+          <t>9922; 26730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1179; 12180</t>
+          <t>1808; 13949</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7510</t>
+          <t>0; 7953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7373</t>
+          <t>0; 8299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11585; 23647</t>
+          <t>12732; 25701</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1174; 11939</t>
+          <t>1183; 11443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>951; 9111</t>
+          <t>937; 8251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1021; 10404</t>
+          <t>1086; 12910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25914; 45066</t>
+          <t>26261; 48921</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>32923</t>
         </is>
       </c>
     </row>
@@ -2635,52 +2635,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4987</t>
+          <t>0; 5263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8380; 19196</t>
+          <t>7939; 18491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7313</t>
+          <t>0; 7501</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 8337</t>
+          <t>0; 10134</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 6197</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15138; 26103</t>
+          <t>14726; 25818</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6536</t>
+          <t>0; 6693</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 8396</t>
+          <t>0; 8560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>894; 7826</t>
+          <t>903; 7762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26144; 42071</t>
+          <t>26224; 42530</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>31695</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5886</t>
+          <t>0; 6154</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8689; 24537</t>
+          <t>9304; 28313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,37 +2858,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1850; 10624</t>
+          <t>1863; 11147</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>882; 8409</t>
+          <t>879; 8323</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10108; 20036</t>
+          <t>10106; 20555</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5894</t>
+          <t>0; 5787</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1879; 10955</t>
+          <t>1813; 10752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>871; 7619</t>
+          <t>873; 7652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21459; 41040</t>
+          <t>23685; 46307</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11476</t>
         </is>
       </c>
     </row>
@@ -3041,27 +3041,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>850; 9786</t>
+          <t>844; 10074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 13888</t>
+          <t>0; 10776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1026; 11154</t>
+          <t>1636; 10897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1615; 6730</t>
+          <t>1637; 7387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7327</t>
+          <t>0; 8508</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4981; 10889</t>
+          <t>4806; 11104</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2088; 13659</t>
+          <t>2140; 13386</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 10973</t>
+          <t>0; 12137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1008; 11036</t>
+          <t>1012; 11095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7759; 15347</t>
+          <t>7873; 16214</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>30936</t>
         </is>
       </c>
     </row>
@@ -3254,22 +3254,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6493</t>
+          <t>0; 6697</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>809; 8042</t>
+          <t>808; 8015</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8264; 18596</t>
+          <t>8324; 18367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7132</t>
+          <t>0; 7375</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5981</t>
+          <t>0; 6913</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13710; 23264</t>
+          <t>13838; 24534</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8266</t>
+          <t>0; 8298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6769</t>
+          <t>0; 6105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1080; 9835</t>
+          <t>957; 9959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24773; 38948</t>
+          <t>24805; 39021</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>22283</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4650</t>
+          <t>0; 4118</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1015; 12871</t>
+          <t>1959; 13690</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7716</t>
+          <t>0; 6649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2149; 9401</t>
+          <t>2731; 12701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4970</t>
+          <t>0; 5001</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3011; 13618</t>
+          <t>2192; 13415</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>958; 8411</t>
+          <t>969; 8336</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2054; 58498</t>
+          <t>10181; 24015</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5534</t>
+          <t>0; 5584</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5402; 21078</t>
+          <t>6104; 21119</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1992; 11433</t>
+          <t>2003; 11555</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3953; 55304</t>
+          <t>15093; 32975</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>31660</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1024; 12806</t>
+          <t>1005; 11819</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6541</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1085; 10056</t>
+          <t>1097; 9442</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3023; 10483</t>
+          <t>3314; 13165</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1639; 12865</t>
+          <t>1161; 12187</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 7744</t>
+          <t>0; 7510</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3232; 16071</t>
+          <t>3871; 16662</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14727; 27535</t>
+          <t>17446; 33314</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4149; 18257</t>
+          <t>3591; 17161</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1046; 10364</t>
+          <t>1052; 10355</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5587; 19842</t>
+          <t>6623; 22160</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19775; 34838</t>
+          <t>23502; 41704</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5479; 20075</t>
+          <t>6058; 20774</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9727; 28419</t>
+          <t>9478; 27855</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10835; 27175</t>
+          <t>10481; 28089</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66767; 99445</t>
+          <t>70340; 105299</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10194; 28173</t>
+          <t>10648; 29809</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18056; 41584</t>
+          <t>19644; 43059</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14921; 33490</t>
+          <t>14748; 33957</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64709; 162854</t>
+          <t>115664; 147593</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18664; 41428</t>
+          <t>18714; 41885</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31692; 61375</t>
+          <t>32674; 62658</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28035; 54523</t>
+          <t>29164; 56166</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>118878; 245815</t>
+          <t>194694; 241368</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
